--- a/temp/pages/ValueSet-botswana-amr-gram-stain-result-vs.xlsx
+++ b/temp/pages/ValueSet-botswana-amr-gram-stain-result-vs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/ValueSet/botswana-amr-gram-stain-result-vs</t>
+    <t>http://bw.health.gov/fhir/amr/ValueSet/botswana-amr-gram-stain-result-vs</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-09T10:14:37-04:00</t>
+    <t>2026-03-13T21:27:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,13 +108,13 @@
     <t>87172008</t>
   </si>
   <si>
-    <t>Gram-negative</t>
-  </si>
-  <si>
-    <t>411933009</t>
-  </si>
-  <si>
-    <t>Gram-variable</t>
+    <t>Gram-negative bacillus</t>
+  </si>
+  <si>
+    <t>301780001</t>
+  </si>
+  <si>
+    <t>Gram-variable bacterium</t>
   </si>
   <si>
     <t>58296003</t>
